--- a/www/download/COUNTRY.TWN.rpO2.xlsx
+++ b/www/download/COUNTRY.TWN.rpO2.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>China: Taiwan</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Ochoa 2</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,2523 +852,4084 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>26.4760398769361</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>27.4574416266748</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>28.6615076395938</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>33.4448165399382</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>32.2684732083258</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.059</t>
+          <t>31.2207295837448</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>33.7952018675018</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>34.578145867322</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>34.4234076826823</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.064</t>
+          <t>33.4224592164426</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.067</t>
+          <t>32.1646824788283</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.068</t>
+          <t>32.5309040569911</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>32.8407230902673</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>31.5169997719211</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.077</t>
+          <t>33.0489991420892</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>9.368</t>
+          <t>-0.812245611919432</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>9.275</t>
+          <t>-0.821285777282774</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>9.39</t>
+          <t>-0.785127861259192</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>9.425</t>
+          <t>-0.793210833469458</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>9.458</t>
+          <t>-0.849546499834887</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>9.597</t>
+          <t>-0.89190627080252</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>9.383</t>
+          <t>-0.888037590889266</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>9.454</t>
+          <t>-0.897844803048484</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>9.574</t>
+          <t>-0.898529949873383</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>9.784</t>
+          <t>-0.888144124631377</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>9.943</t>
+          <t>-0.889455730954608</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>10.113</t>
+          <t>-0.878256078609152</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>10.292</t>
+          <t>-0.830499645541232</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>10.404</t>
+          <t>-0.817910981554389</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>10.279</t>
+          <t>-0.734018184636448</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>6.476</t>
+          <t>-0.746612189465532</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>6.448</t>
+          <t>-0.75971008422223</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>6.585</t>
+          <t>-0.712338659360383</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>6.664</t>
+          <t>-0.724459154505337</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>6.722</t>
+          <t>-0.800713737933811</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>6.855</t>
+          <t>-0.857741886402898</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>6.73</t>
+          <t>-0.853731995671135</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>6.774</t>
+          <t>-0.867663795135374</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>6.923</t>
+          <t>-0.868607875405683</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>7.165</t>
+          <t>-0.855471056710801</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>7.366</t>
+          <t>-0.86005802130875</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>7.553</t>
+          <t>-0.846728363222668</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>7.745</t>
+          <t>-0.788306798507914</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>7.93</t>
+          <t>-0.770986599592613</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>7.907</t>
+          <t>-0.664737506000509</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>21651.582</t>
+          <t>-0.734391827678723</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>21306.613</t>
+          <t>-0.747842966969444</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>21621.853</t>
+          <t>-0.698122957565003</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>21389.203</t>
+          <t>-0.710386876556299</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>21466.651</t>
+          <t>-0.790478248615635</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>21802.7</t>
+          <t>-0.850460146266499</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>20446.521</t>
+          <t>-0.846482190617826</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>20645.819</t>
+          <t>-0.861241098126767</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>20895.479</t>
+          <t>-0.861838409706148</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>21547.134</t>
+          <t>-0.84733746762008</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>21808.029</t>
+          <t>-0.85280957036099</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>22052.318</t>
+          <t>-0.838490871959574</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>22426.051</t>
+          <t>-0.778151710000684</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>22584.97</t>
+          <t>-0.764307251605391</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>21729.434</t>
+          <t>-0.635623833752538</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>15097.83</t>
+          <t>858003593634.243</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>14946.957</t>
+          <t>805607806459.304</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>15293.409</t>
+          <t>729496572038.025</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>15229.189</t>
+          <t>802681842052.994</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>15348.731</t>
+          <t>1073502421990.41</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>15665.324</t>
+          <t>1821161561458.36</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>14693.148</t>
+          <t>1711815298029.21</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>14840.401</t>
+          <t>1938413456359.72</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>15160.842</t>
+          <t>2116320307000.78</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>15843.53</t>
+          <t>2397626982932.91</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>16187.971</t>
+          <t>2633884047023.11</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>16526.11</t>
+          <t>2801646653175.31</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>16946.724</t>
+          <t>2359821096917.41</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>17266.618</t>
+          <t>2315569426525.06</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>16712.116</t>
+          <t>1318697380754.27</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>27.87</t>
+          <t>179895762030.367</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>28.71</t>
+          <t>178995371396.701</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>29.53</t>
+          <t>158629274823.416</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>30.33</t>
+          <t>167829076288.641</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>31.11</t>
+          <t>228092673311.701</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>31.88</t>
+          <t>343441327008.951</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>32.63</t>
+          <t>339514359245.823</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>33.36</t>
+          <t>352705783705.003</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>34.14</t>
+          <t>352833440434.122</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>34.92</t>
+          <t>349424962447.308</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>35.42</t>
+          <t>374803710801.789</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>37.21</t>
+          <t>381077485004.651</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>36.68</t>
+          <t>301136602221.356</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>38.05</t>
+          <t>299461473138.367</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>41.28</t>
+          <t>200801273529.945</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>30.83</t>
+          <t>51827196.6287729</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>31.16</t>
+          <t>47095599.1847612</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>31.49</t>
+          <t>42394914.3907843</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>31.82</t>
+          <t>51914717.1810359</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>32.15</t>
+          <t>63171531.2047528</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>32.49</t>
+          <t>89431389.0201876</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>32.83</t>
+          <t>98818511.002553</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>33.17</t>
+          <t>109891974.220968</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>33.14</t>
+          <t>112545085.284224</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>33.12</t>
+          <t>107260351.233288</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>32.96</t>
+          <t>107252167.715845</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>32.34</t>
+          <t>106863380.120653</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>32.95</t>
+          <t>83007952.9170775</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>32.58</t>
+          <t>78801735.4901071</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>33.24</t>
+          <t>55271181.743487</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>41.3</t>
+          <t>11276.5006842359</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>40.13</t>
+          <t>10221.2631061874</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>38.98</t>
+          <t>9851.99794269159</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>37.85</t>
+          <t>9578.85224211528</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>36.73</t>
+          <t>8652.00406857869</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>35.63</t>
+          <t>6983.00879308644</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>34.55</t>
+          <t>6613.56400731105</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>33.47</t>
+          <t>6490.7699261011</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>32.72</t>
+          <t>6677.98121629081</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>31.96</t>
+          <t>7191.96549801333</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>31.62</t>
+          <t>7321.57696130247</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>30.45</t>
+          <t>8699.8076089221</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>30.38</t>
+          <t>12236.4803722528</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>29.38</t>
+          <t>14691.4086464809</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>25.48</t>
+          <t>16375.9478729838</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>21.42</t>
+          <t>359707.816303513</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>22.18</t>
+          <t>350707.229208491</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>22.93</t>
+          <t>312827.985594148</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>23.68</t>
+          <t>338564.765065738</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>24.44</t>
+          <t>421642.458005856</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>25.19</t>
+          <t>564148.641834888</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>25.95</t>
+          <t>504384.532912393</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>26.7</t>
+          <t>600183.757890379</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>27.43</t>
+          <t>669949.338885286</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>28.16</t>
+          <t>819840.872775807</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>28.99</t>
+          <t>870606.30575207</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>30.83</t>
+          <t>981415.917602628</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>30.46</t>
+          <t>1053507.9060905</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>31.76</t>
+          <t>1156718.11711127</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>34.17</t>
+          <t>760797.926939921</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>32.27</t>
+          <t>-0.76425162512627</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>32.7</t>
+          <t>-0.776960206138772</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>33.12</t>
+          <t>-0.733855606440929</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>33.54</t>
+          <t>-0.745439946952072</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>33.97</t>
+          <t>-0.816225564790871</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>34.39</t>
+          <t>-0.869075003526944</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>34.81</t>
+          <t>-0.865708017095591</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>35.23</t>
+          <t>-0.878514675242851</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>35.27</t>
+          <t>-0.87957177384605</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>35.3</t>
+          <t>-0.867305097589954</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>35.04</t>
+          <t>-0.871028909550987</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>34.52</t>
+          <t>-0.85882102948589</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>35.13</t>
+          <t>-0.804986973391135</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>35.17</t>
+          <t>-0.791568976290118</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>35.75</t>
+          <t>-0.693656226088707</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>37840.9451226263</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>45.13</t>
+          <t>39172.5425932418</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>43.95</t>
+          <t>42526.5860996838</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>42.77</t>
+          <t>43035.5940772088</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>41.6</t>
+          <t>49723.1898636696</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>40.42</t>
+          <t>58566.5527948832</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>39.24</t>
+          <t>53069.9843390756</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>38.07</t>
+          <t>52521.9195117726</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>37.3</t>
+          <t>55437.0219881852</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>36.54</t>
+          <t>63853.6183875367</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>35.97</t>
+          <t>66840.5141894893</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>34.65</t>
+          <t>67763.8504520565</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>34.41</t>
+          <t>73131.7358711163</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>33.07</t>
+          <t>80320.2970282769</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>30.08</t>
+          <t>76776.1213821351</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>26.4760398769361</t>
+          <t>27780.0161787968</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>27.4574416266748</t>
+          <t>27758.8302326068</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>28.6615076395938</t>
+          <t>24089.1931019925</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>33.4448165399382</t>
+          <t>25183.2408625437</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>32.2684732083258</t>
+          <t>33931.5685732896</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>31.2207295837448</t>
+          <t>50097.5107120783</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>33.7952018675018</t>
+          <t>50450.7708481709</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>34.578145867322</t>
+          <t>52065.7800273544</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>34.4234076826823</t>
+          <t>50967.2013525738</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>33.4224592164426</t>
+          <t>48766.9992959201</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>32.1646824788283</t>
+          <t>50885.1476575758</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>32.5309040569911</t>
+          <t>50451.1811407562</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>32.8407230902673</t>
+          <t>38882.6504097551</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>31.5169997719211</t>
+          <t>37764.649378708</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>33.0489991420892</t>
+          <t>25395.0676552607</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>353931342804.189</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.146</t>
+          <t>367172792593.295</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>328434859409.375</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.135</t>
+          <t>347559104411.249</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.144</t>
+          <t>489737041329.632</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.155</t>
+          <t>756593461851.41</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.141</t>
+          <t>751882406796.305</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.138</t>
+          <t>829697950061.919</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.142</t>
+          <t>832475912319.894</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.152</t>
+          <t>819141999428.826</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.166</t>
+          <t>885600141446.106</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.172</t>
+          <t>904194194088.536</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.176</t>
+          <t>747068725410.267</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.184</t>
+          <t>684334007100.44</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.169</t>
+          <t>468076897704.909</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.171</t>
+          <t>368375946712.797</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.179</t>
+          <t>385161475359.016</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.182</t>
+          <t>345624890240.681</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.164</t>
+          <t>371155358875.709</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.176</t>
+          <t>519196422846.369</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.188</t>
+          <t>811474629934.685</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.172</t>
+          <t>802096908207.531</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.168</t>
+          <t>879748259570.185</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.173</t>
+          <t>887767997575.987</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.184</t>
+          <t>886193101010.095</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.201</t>
+          <t>961317627570.142</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.208</t>
+          <t>984221127029.081</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.211</t>
+          <t>811607415254.495</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.221</t>
+          <t>747103367144.774</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.204</t>
+          <t>503510958209.641</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.505</t>
+          <t>-14444603908.6088</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0.516</t>
+          <t>-17988682765.7205</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0.539</t>
+          <t>-17190030831.3067</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0.517</t>
+          <t>-23596254464.4604</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.576</t>
+          <t>-29459381516.7372</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.634</t>
+          <t>-54881168083.2753</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.603</t>
+          <t>-50214501411.2264</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.613</t>
+          <t>-50050309508.266</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.655</t>
+          <t>-55292085256.0931</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0.762</t>
+          <t>-67051101581.2695</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>0.817</t>
+          <t>-75717486124.0358</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>0.873</t>
+          <t>-80026932940.5452</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>-64538689844.2279</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>1.064</t>
+          <t>-62769360044.3343</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>1.003</t>
+          <t>-35434060504.7317</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>6549.09366811728</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.596</t>
+          <t>6191.32377290943</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.617</t>
+          <t>6411.20368945714</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.559</t>
+          <t>6410.64712988788</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.601</t>
+          <t>6235.75485031611</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.668</t>
+          <t>6559.01641328774</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.588</t>
+          <t>6775.13405625681</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.607</t>
+          <t>6325.22819535743</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.642</t>
+          <t>6137.88965092167</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.738</t>
+          <t>6471.13221240289</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.796</t>
+          <t>6562.71298105661</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.838</t>
+          <t>7122.64581467283</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.901</t>
+          <t>7582.62333898078</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0.946</t>
+          <t>7871.32453004888</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>7779.62086424516</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.262</t>
+          <t>6258.46209487372</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.278</t>
+          <t>5679.93087545164</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.289</t>
+          <t>5659.77230252937</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.267</t>
+          <t>5729.86208332856</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.289</t>
+          <t>5616.30673471862</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.311</t>
+          <t>5906.51753848903</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.283</t>
+          <t>6094.06538399683</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.289</t>
+          <t>5846.79207308797</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.296</t>
+          <t>5940.50256579918</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.321</t>
+          <t>5915.89032278693</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.345</t>
+          <t>6061.44693780986</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.356</t>
+          <t>6609.65767953415</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.374</t>
+          <t>7048.6353737773</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>7437.74358514568</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.358</t>
+          <t>7466.25710448326</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>-81.22</t>
+          <t>126915.300584837</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>-82.13</t>
+          <t>133807.570225189</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>-78.51</t>
+          <t>141549.403621721</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-79.32</t>
+          <t>129583.20936143</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-84.95</t>
+          <t>140573.515905248</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-89.19</t>
+          <t>171723.904470568</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>-88.8</t>
+          <t>145946.618825458</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>-89.78</t>
+          <t>156566.353351376</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>-89.85</t>
+          <t>172957.536973781</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-88.81</t>
+          <t>206297.20752308</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>-88.95</t>
+          <t>226720.555872909</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>-87.83</t>
+          <t>250928.003961118</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>-83.05</t>
+          <t>277126.017640646</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>-81.79</t>
+          <t>288769.510145104</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>-73.4</t>
+          <t>229938.549269187</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>-74.66</t>
+          <t>292245459508.717</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>-75.97</t>
+          <t>307166144129.552</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>-71.23</t>
+          <t>277701493256.189</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-72.45</t>
+          <t>307986883195.861</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-80.07</t>
+          <t>431242244139.423</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-85.77</t>
+          <t>823901409175.727</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>-85.37</t>
+          <t>759236718859.422</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>-86.77</t>
+          <t>836286037055.089</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>-86.86</t>
+          <t>925822266834.691</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>-85.55</t>
+          <t>1023287548567.83</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>-86.01</t>
+          <t>1138177531945.55</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>-84.67</t>
+          <t>1232606922402.08</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>-78.83</t>
+          <t>999195054397.517</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>-77.1</t>
+          <t>995550969562.563</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>-66.47</t>
+          <t>561577646321.437</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>-73.44</t>
+          <t>115491.205204335</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>-74.78</t>
+          <t>116964.727993192</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>-69.81</t>
+          <t>126404.927715789</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-71.04</t>
+          <t>118725.571668396</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-79.05</t>
+          <t>125228.890666358</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-85.05</t>
+          <t>155143.66271924</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>-84.65</t>
+          <t>123737.886028629</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>-86.12</t>
+          <t>128581.844309189</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>-86.18</t>
+          <t>142925.572710745</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-84.73</t>
+          <t>185090.771689476</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>-85.28</t>
+          <t>200893.328272577</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>-83.85</t>
+          <t>218687.456232123</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>-77.82</t>
+          <t>235846.043363277</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>-76.43</t>
+          <t>258045.085694861</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>-63.56</t>
+          <t>189322.125283643</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>58629.273</t>
+          <t>598873938505.688</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>52681.359</t>
+          <t>607459707168.993</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>53145.262</t>
+          <t>554125071641.969</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>54003.95</t>
+          <t>614779187559.19</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>53119.029</t>
+          <t>845356102129.095</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>56684.849</t>
+          <t>1463967163758.87</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>57180.615</t>
+          <t>1343831135170.79</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>55275.572</t>
+          <t>1464026323321.53</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>56874.372</t>
+          <t>1550284926329.74</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>57881.071</t>
+          <t>1707751690958.49</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>60268.967</t>
+          <t>1851597263096.03</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>66843.468</t>
+          <t>1936953165052.52</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>72544.555</t>
+          <t>1555814388271</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>77382.284</t>
+          <t>1555998374828.24</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>76745.657</t>
+          <t>897979762131.854</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>42410.134</t>
+          <t>11424.0953805027</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>39923.091</t>
+          <t>16842.8422319973</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>42218.292</t>
+          <t>15144.4759059314</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>42722.579</t>
+          <t>10857.6376930343</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>41917.602</t>
+          <t>15344.6252388895</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>44965.055</t>
+          <t>16580.2417513284</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>45594.057</t>
+          <t>22208.7327968289</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>42848.577</t>
+          <t>27984.5090421867</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>42491.105</t>
+          <t>30031.9642630362</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>46366.911</t>
+          <t>21206.4358336036</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>48338.843</t>
+          <t>25827.2276003316</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>53800.127</t>
+          <t>32240.5477289959</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>58725.56</t>
+          <t>41279.9742773682</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>62417.061</t>
+          <t>30724.4244502436</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>61514.22</t>
+          <t>40616.4239855442</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>858003.594</t>
+          <t>-306628478996.972</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>805607.806</t>
+          <t>-300293563039.441</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>729496.572</t>
+          <t>-276423578385.78</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>802681.842</t>
+          <t>-306792304363.329</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>1073502.422</t>
+          <t>-414113857989.672</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>1821161.561</t>
+          <t>-640065754583.144</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1711815.298</t>
+          <t>-584594416311.37</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>1938413.456</t>
+          <t>-627740286266.438</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2116320.307</t>
+          <t>-624462659495.053</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2397626.983</t>
+          <t>-684464142390.653</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2633884.047</t>
+          <t>-713419731150.482</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>2801646.653</t>
+          <t>-704346242650.442</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>2359821.097</t>
+          <t>-556619333873.48</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>2315569.427</t>
+          <t>-560447405265.679</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>1318697.381</t>
+          <t>-336402115810.418</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>115885.19263</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.351</t>
+          <t>120899.79259</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.313</t>
+          <t>122402.31903</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.339</t>
+          <t>111252.9351</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.422</t>
+          <t>117455.72698</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.564</t>
+          <t>121887.86232</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.504</t>
+          <t>107332.51486</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>111310.5662</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>112697.38423</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>120663.95146</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.871</t>
+          <t>127889.89906</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.981</t>
+          <t>131144.28038</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>1.054</t>
+          <t>139969.05593</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>1.157</t>
+          <t>133690.32676</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.761</t>
+          <t>127911.08753</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>26897.603</t>
+          <t>0.105268843803967</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>23479.212</t>
+          <t>0.115713310351518</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>22974.283</t>
+          <t>0.119765472648056</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>22709.896</t>
+          <t>0.114393255856194</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>22028.017</t>
+          <t>0.109815170168258</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>22542.263</t>
+          <t>0.100895389063207</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>22445.573</t>
+          <t>0.0973426790902998</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>20963.239</t>
+          <t>0.112147313142895</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>21095.248</t>
+          <t>0.104438739623569</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>21032.924</t>
+          <t>0.0955865599994396</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>22150.293</t>
+          <t>0.0949477876831069</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>24835.329</t>
+          <t>0.0917519742672653</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>27409.291</t>
+          <t>0.0961898461420713</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>29409.911</t>
+          <t>0.0746390784801517</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>28384.567</t>
+          <t>0.0776081605524416</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>139276.624928551</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>146385.999045722</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>149823.721510242</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>134565.297386867</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>143785.405090095</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>154526.466639178</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>141412.000266344</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>137943.195527433</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>142429.711039491</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>152115.099336601</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>165805.900278924</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>172048.156420619</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>175788.537823953</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>183824.014436678</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>169371.52751886</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>179895.762</t>
+          <t>170674.531036294</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>178995.371</t>
+          <t>179262.534251722</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>158629.275</t>
+          <t>182091.650982684</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>167829.076</t>
+          <t>164311.131679755</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>228092.673</t>
+          <t>176098.037946597</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>343441.327</t>
+          <t>188365.268356586</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>339514.359</t>
+          <t>171574.566746385</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>352705.784</t>
+          <t>167528.333807679</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>352833.44</t>
+          <t>172506.401579701</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>349424.962</t>
+          <t>184264.398670204</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>374803.711</t>
+          <t>200746.334689084</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>381077.485</t>
+          <t>207723.236472464</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>301136.602</t>
+          <t>211172.142171429</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>299461.473</t>
+          <t>220585.827149092</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>200801.274</t>
+          <t>203574.600826775</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>-76.43</t>
+          <t>504927.311922058</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>-77.7</t>
+          <t>516427.067409121</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>-73.39</t>
+          <t>538741.153781766</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-74.54</t>
+          <t>517485.758141669</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-81.62</t>
+          <t>575972.257501595</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-86.91</t>
+          <t>634283.138830458</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>-86.57</t>
+          <t>603069.804562106</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>-87.85</t>
+          <t>612526.70345318</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>-87.96</t>
+          <t>655216.869322225</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>-86.73</t>
+          <t>761752.847290309</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>-87.1</t>
+          <t>817496.487232387</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>-85.88</t>
+          <t>872795.86096111</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>-80.5</t>
+          <t>930138.657206178</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>-79.16</t>
+          <t>1064420.98925107</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>-69.37</t>
+          <t>1002614.26620783</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>51.827</t>
+          <t>170674.531036294</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>47.096</t>
+          <t>182782.359036392</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>42.395</t>
+          <t>189687.876484339</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>51.915</t>
+          <t>195584.619276153</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>63.172</t>
+          <t>202943.629853673</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>89.431</t>
+          <t>208005.46861129</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>98.819</t>
+          <t>204855.427334524</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>109.892</t>
+          <t>204723.854000435</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>112.545</t>
+          <t>207934.802040712</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>107.26</t>
+          <t>209993.349097749</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>107.252</t>
+          <t>218498.744024458</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>106.863</t>
+          <t>224995.141507731</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>83.008</t>
+          <t>228990.543360731</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>78.802</t>
+          <t>225733.673686465</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>55.271</t>
+          <t>222874.170231128</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>139276.624928551</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>149580.772791529</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>156280.98911373</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>160744.107966953</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>166692.618398156</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>171465.578402718</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>169299.65409321</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>168927.202540183</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>171967.546960885</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>173757.91829522</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>181001.525914776</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>186544.612446131</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>190964.353713897</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>188647.256825312</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>186258.695058692</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>90994.0594537061</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>98930.0281182777</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>107049.175017316</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>102232.474810245</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>112973.681333403</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>122562.796863414</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>111774.414793615</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>121215.143532321</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>123867.046000299</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>136666.952629796</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>144459.997090916</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>147844.593827536</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>162601.630198571</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>159767.698780908</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>154587.170326161</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>42410133545.3304</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>39923090738.434</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>42218292148.5933</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>42722578563.0212</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>41917602213.1982</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>44965054527.3485</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>45594056527.6413</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>42848576677.127</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>42491105359.2768</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>46366911291.5793</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>48338843286.4434</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>53800127019.0627</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>58725560221.8966</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>62417061407.8992</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>61514219939.3571</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>58629272904.777</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>52681358869.8139</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>53145261920.7508</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>54003950135.3717</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>53119029096.9688</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>56684848816.8793</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>57180615498.0422</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>55275572258.9736</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>56874371564.9614</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>57881070918.1474</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>60268966902.6434</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>66843468113.1289</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>72544555266.916</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>77382284259.8557</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>76745656776.9835</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>26897603199.5081</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>23479211902.1984</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>22974283177.6034</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>22709896468.2921</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>22028017213.013</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>22542263251.6356</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>22445573374.0289</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>20963239343.7534</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>21095247711.2988</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>21032923718.4479</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>22150292996.9798</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>24835328665.0834</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>27409290777.5268</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>29409910842.6989</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>28384566785.4685</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>9368000</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>9275000</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>9390000</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>9425000</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>9458000</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>9597000</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>9383000</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>9454000</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>9574000</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>9784000</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>9943000</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>10113000</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>10292000</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>10404000</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>10279000</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>6475725.60334481</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>6448231.78414933</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>6585080.46125861</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>6664316.05068995</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>6722137.61114634</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>6855456.93044083</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>6729616.88271473</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>6774234.12305928</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>6922754.85156308</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>7165193.00945672</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>7365679.92931801</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>7553390.75098092</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>7744755.02693112</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>7929677.04096322</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>7907097.403946</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>21651582189.6789</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>21306613261.9126</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>21621852706.019</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>21389202863.1726</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>21466650718.1514</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>21802699817.3186</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>20446520684.4522</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>20645819397.8129</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>20895478594.8239</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>21547134118.0846</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>21808029300.3046</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>22052317653.749</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>22426050893.6546</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>22584970372.8856</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>21729434381.5685</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>15097830216.4054</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>14946956845.1698</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>15293409103.6755</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>15229189326.1391</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>15348730504.7165</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>15665324405.3071</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>14693147569.6039</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>14840400700.7909</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>15160841982.1177</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>15843529969.6984</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>16187970505.3992</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>16526110478.8122</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>16946724328.8859</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>17266618144.9646</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>16712115566.2901</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>0.278661046608263</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>0.287068902069005</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0.295280418344885</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>0.303300390719474</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>0.311133312462363</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>0.318783395141901</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>0.326254586924336</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>0.333550589078339</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0.341414762121223</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>0.349165485148323</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>0.354232247339983</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>0.372099401365079</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>0.366770912127975</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>0.380458193364835</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>0.412754001468868</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>0.308343832456194</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>0.311591700769992</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0.314870815048877</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>0.31818036630264</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>0.321519643434556</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>0.324888026905767</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>0.328284983091023</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>0.331710059251875</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0.331430527503408</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>0.33119171473992</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>0.32956276626521</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>0.32336906100886</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>0.329465738342722</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>0.325787181809133</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>0.332430771654221</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>0.412995120935543</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>0.401339397161003</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0.389848766606239</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>0.378519242977886</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>0.367347044103081</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>0.356328577952332</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>0.345460429984641</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>0.334739351669787</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0.327154710375368</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>0.319642800111757</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>0.316204986394807</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>0.304531537626061</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>0.303763349529303</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>0.293754624826032</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>0.254815226876912</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>0.214223984649701</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>0.221762082415447</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0.229300180181193</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>0.236838277946938</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>0.244376375712684</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>0.25191447347843</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>0.259452571244176</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>0.266990669009922</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0.274297445852658</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>0.281604222695395</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>0.289922249231759</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>0.308288891565255</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>0.304642425381812</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>0.317551555991869</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>0.341667640070491</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>0.3227469521659</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>0.32697344651853</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0.33119994087116</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>0.335426435223791</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>0.339652929576421</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>0.343879423929051</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>0.348105918281681</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>0.352332412634311</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0.352659077651124</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>0.352985742667937</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>0.35040809984152</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>0.345171811253209</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>0.351305333899944</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>0.351708638479808</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>0.357530055963773</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>0.463029063184399</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>0.451264471066023</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0.439499878947647</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>0.427735286829271</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>0.415970694710895</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>0.404206102592519</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>0.392441510474143</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>0.380676918355767</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0.373043476496218</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>0.365410034636669</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>0.359669650926721</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>0.346539297181535</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>0.344052240718244</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>0.330739805528323</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>0.300802303965736</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>579827.12367</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>595756.99404</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>617079.60598</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>559258.11173</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>600785.57935</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>667886.93136</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>588049.75076</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>607155.39682</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>642358.59517</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>738392.64111</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>795818.39608</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>837615.21176</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>900791.7699</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>945759.69106</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>810483.6867</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>261668.59049</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>278192.56237</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>289140.826</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>266543.60649</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>289071.71928</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>310928.06522</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>283348.98154</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>288743.47734</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>296373.44758</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>320931.3513</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>345206.33178</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>355567.8303</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>373773.77237</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>380353.52593</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>357822.52825</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>13368475.5407106</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>14531159.0825348</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>15801491.4409056</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>17145061.2032804</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>18435286.2317739</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>19817700.7057358</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>20624728.998767</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>21389003.3752959</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>22104438.7933364</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>23091470.7347447</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>24047762.2097772</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>24941454.4203983</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>25794657.7022577</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>26322561.8895612</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>26528061.3447381</t>
         </is>
       </c>
     </row>
@@ -3374,7 +4940,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3397,36 +4963,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3438,331 +5019,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3799,6 +5744,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Ochoa 2</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpO2</t>
